--- a/artfynd/A 29185-2025 artfynd.xlsx
+++ b/artfynd/A 29185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109588346</v>
+        <v>109589503</v>
       </c>
       <c r="B2" t="n">
-        <v>101097</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ältån, Upl</t>
+          <t>Findasängen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695748</v>
+        <v>695588</v>
       </c>
       <c r="R2" t="n">
-        <v>6608099</v>
+        <v>6608378</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109588430</v>
+        <v>109589524</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +799,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ältån, Upl</t>
+          <t>Findasängen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695717</v>
+        <v>695585</v>
       </c>
       <c r="R3" t="n">
-        <v>6608161</v>
+        <v>6608387</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109820603</v>
+        <v>109589562</v>
       </c>
       <c r="B4" t="n">
-        <v>97847</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,48 +912,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännmora, Upl</t>
+          <t>Findasängen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695701</v>
+        <v>695595</v>
       </c>
       <c r="R4" t="n">
-        <v>6608271</v>
+        <v>6608398</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,6 +1011,451 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109820603</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännmora, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695701</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6608271</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109588346</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ältån, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695748</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6608099</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109588430</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ältån, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>695717</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6608161</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109820541</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ältån, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>695759</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6608178</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29185-2025 artfynd.xlsx
+++ b/artfynd/A 29185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109820603</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109588346</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109588430</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,8 +1491,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109820541</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>